--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aadarsh/Documents/Coding/HackClub/tars-display/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA263F69-7AFD-504C-9131-902A3BC9D12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D626B2E8-7B3F-8F45-94D2-C776C6B96F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20480" yWindow="620" windowWidth="20480" windowHeight="24980" xr2:uid="{76F3C5F8-0592-3545-9B77-C38043100BE4}"/>
+    <workbookView xWindow="15860" yWindow="620" windowWidth="25100" windowHeight="24980" xr2:uid="{76F3C5F8-0592-3545-9B77-C38043100BE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="49">
   <si>
     <t>Component</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>https://www.amazon.com/Waveshare-Resolution-Horizontal-Pinheader-Raspberry/dp/B0BFQF8GT3/</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -642,6 +645,12 @@
       <c r="I2" s="1">
         <v>6.22</v>
       </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -672,6 +681,12 @@
       <c r="I3" s="1">
         <v>25.82</v>
       </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -702,6 +717,12 @@
       <c r="I4" s="1">
         <v>25.82</v>
       </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -732,6 +753,12 @@
       <c r="I5" s="1">
         <v>25.82</v>
       </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -762,6 +789,12 @@
       <c r="I6" s="1">
         <v>25.82</v>
       </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -774,8 +807,7 @@
         <v>7.49</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="0"/>
-        <v>14.98</v>
+        <v>7.49</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -791,6 +823,12 @@
       </c>
       <c r="I7" s="1">
         <v>59.84</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -801,11 +839,11 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>11.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
-        <v>11.99</v>
+        <f>B8*C8</f>
+        <v>19.989999999999998</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
@@ -821,6 +859,12 @@
       </c>
       <c r="I8" s="1">
         <v>59.84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -852,6 +896,12 @@
       <c r="I9" s="1">
         <v>59.84</v>
       </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -882,6 +932,12 @@
       <c r="I10" s="1">
         <v>25.82</v>
       </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -912,6 +968,12 @@
       <c r="I11" s="1">
         <v>25.82</v>
       </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -942,6 +1004,12 @@
       <c r="I12" s="1">
         <v>25.82</v>
       </c>
+      <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -963,6 +1031,12 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -984,6 +1058,12 @@
       <c r="I14" s="1">
         <v>0</v>
       </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1005,6 +1085,12 @@
       <c r="I15" s="1">
         <v>0</v>
       </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1026,8 +1112,14 @@
       <c r="I16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1056,21 +1148,27 @@
       <c r="I17" s="1">
         <v>59.84</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="1">
         <f>SUM(D2:D17)</f>
-        <v>61.980000000000004</v>
+        <v>62.49</v>
       </c>
       <c r="I18" s="1">
         <f>I2+I3+I7</f>
         <v>91.88</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
